--- a/Intern_Exam_Portal/frontend/public/sample_mcqs_template.xlsx
+++ b/Intern_Exam_Portal/frontend/public/sample_mcqs_template.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MCQs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,15 +30,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0092400E"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -51,23 +43,8 @@
         <fgColor rgb="001A56DB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,31 +52,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,353 +426,1051 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Option_A</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Option_B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Option_C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Option_D</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Correct_Answer</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Question_Mark</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>What does RAM stand for?</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Random Access Memory</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Read Access Mode</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Run After Memory</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Read All Memory</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Which keyword is used to define a function in Python?</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>def</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>fun</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>define</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>What is the time complexity of binary search?</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>O(n)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>O(n log n)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>O(log n)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>O(1)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Which of the following is NOT a Python data type?</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>tuple</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>dict</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Explain the concept of Object-Oriented Programming and its four main principles.</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>5M</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>What is the difference between a stack and a queue? Give a real-world example for each.</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>2M</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Describe the steps involved in the Software Development Life Cycle (SDLC).</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>10M</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>option_c</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>option_d</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>correct_answer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>question_mark</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Write the full question text here.</t>
+          <t>What does HTML stand for?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HyperText Markup Language</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HighText Machine Language</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HyperText and links Markup Language</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>None of the above</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Option_A to Option_D</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fill options for MCQ questions. Leave BLANK for descriptive questions.</t>
+          <t>Which language is used for styling web pages?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Correct_Answer</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enter 'a', 'b', 'c', or 'd' for MCQ. Leave BLANK for descriptive questions.</t>
+          <t>What does CSS stand for?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Computer Style Sheets</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Creative Style Sheets</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cascading Style Sheets</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Colorful Style Sheets</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Question_Mark</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>For DESCRIPTIVE questions only: enter 2M, 5M, or 10M. Leave BLANK for MCQ.</t>
+          <t>Which HTML tag is used for the largest heading?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;h6&gt;</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&lt;heading&gt;</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;h1&gt;</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>&lt;head&gt;</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>What is the correct HTML element for inserting a line break?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>&lt;lb&gt;</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&lt;break&gt;</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>&lt;newline&gt;</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Row Type</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>How the system decides:</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Which symbol is used for comments in Python?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>/*</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Option A-D filled + Correct_Answer filled + Question_Mark blank → auto-graded</t>
+          <t>What does SQL stand for?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Structured Query Language</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Simple Query Language</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Standard Question Language</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Structured Question Language</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Descriptive</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Correct_Answer blank + Question_Mark = 2M/5M/10M → admin-reviewed</t>
+          <t>Which data type stores decimal numbers in Python?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>What is a primary key in a database?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A key for locking the database</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A unique identifier for each record</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The first column</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>An index column</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Which HTTP method is used to send data to a server?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>What does API stand for?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Application Programming Integration</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Application Protocol Interface</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Application Programming Interface</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Automated Program Interface</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Which of the following is NOT a JavaScript framework?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vue</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Django</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>What is a REST API?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A type of database</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A protocol for file transfer</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>An architectural style for APIs over HTTP</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A JavaScript framework</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>What does OOP stand for?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Object Oriented Programming</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open Oriented Protocol</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Object Output Process</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>None of the above</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Which Python keyword is used to create a function?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>define</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>def</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>What is Git used for?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Database management</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Version control</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Web development</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>API testing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Which tag is used to create a hyperlink in HTML?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>&lt;link&gt;</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>&lt;href&gt;</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>&lt;url&gt;</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>What is the time complexity of binary search?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>O(n)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>O(n²)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>O(log n)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>O(1)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Which of these is a NoSQL database?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SQLite</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>What does JSON stand for?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JavaScript Object Numbers</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JavaScript Object Notation</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Java Source Object Network</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JavaScript Output Notation</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Which command is used to install Python packages?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>npm install</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>pip install</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>apt install</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>brew install</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>What is a virtual environment in Python?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A cloud server</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>An isolated Python environment</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A Docker container</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>A virtual machine</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Which HTTP status code means 'Not Found'?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>What is the purpose of an index in a database?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>To encrypt data</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>To backup data</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>To speed up data retrieval</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>To delete data</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Which of the following is a Python web framework?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vue</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Describe Object-Oriented Programming in Python and its four main principles.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Explain the difference between INNER JOIN and LEFT JOIN with an example.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>What is the difference between a stack and a queue? Give a real-world example for each.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Describe the steps involved in the Software Development Life Cycle (SDLC).</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10M</t>
         </is>
       </c>
     </row>
